--- a/www/ig/fhir/tddui/CodeSystem-tddui-observation-periode-scolaire.xlsx
+++ b/www/ig/fhir/tddui/CodeSystem-tddui-observation-periode-scolaire.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:53:20+00:00</t>
+    <t>2026-07-22T14:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
